--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4966-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4966-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07F67DC7-82D9-4CCA-975F-9CC6E2F87C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E9EEF2E-C337-4B31-B4B0-7C7002D7646F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{04A3B84B-E596-4428-9473-A5EB19DD5B64}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{72E7C78A-617C-417C-AD13-AA9B7389F6E7}"/>
   </bookViews>
   <sheets>
     <sheet name="4966-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1546,30 +1546,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E82AA38D-DB3D-4CFE-83F7-AB51BCE57876}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4475BAC-A523-4293-AB75-DD6651FF2BA4}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1603,7 +1603,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1639,7 +1639,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1759,7 +1759,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1867,7 +1867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>29</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>29</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2022</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>29</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>29</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2021</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2020</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>29</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>29</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
         <v>2019</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>2018</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2017</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="47">
         <v>2016</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2015</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="47">
         <v>2014</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2013</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>2012</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2011</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="47">
         <v>2010</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49" t="s">
         <v>55</v>
       </c>
